--- a/data/rooms.xlsx
+++ b/data/rooms.xlsx
@@ -413,50 +413,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>building_name</t>
+          <t>שם מבנה</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>room_number</t>
+          <t>מספר חדר</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>number_of_beds</t>
+          <t>מספר מיטות</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>room_rank</t>
+          <t>דרגת חדר</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>מגדר</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>מזהי דיירים</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>occupant_ids</t>
+          <t>זירה ייעודית</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -467,29 +467,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>סמנכ"ל</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["1001"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -500,29 +500,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>סמנכ"ל</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["1002"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -533,29 +533,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>סמנכ"ל</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["1003"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,29 +566,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>סמנכ"ל</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Exec</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["1004"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -599,29 +599,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2001,2011</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["2001", "2011"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -632,29 +632,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["2002"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -665,29 +665,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Exec</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>בנים</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["2009"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -698,29 +694,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Exec</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>בנות</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["2010"]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -731,29 +723,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3001,3011,3021</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["3001", "3011", "3021"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -764,29 +756,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3002,3012</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["3002", "3012"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -797,29 +789,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>4001,4003,4021,4031,4041,4043,4045,4071</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["4001", "4003", "4021", "4031", "4041", "4043", "4045", "4071"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -830,29 +822,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>4002,4004,4022,4032,4042,4044,4046,4072</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["4002", "4004", "4022", "4032", "4042", "4044", "4046", "4072"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -863,29 +855,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Exec</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>בנים</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>א</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -896,29 +884,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Exec</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>בנות</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>הנהלה</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -929,29 +913,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["2003"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -962,29 +946,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>2004,2012</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["2004", "2012"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -995,29 +979,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3003,3013</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["3003", "3013"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1028,29 +1012,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3004,3014,3022</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["3004", "3014", "3022"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1061,29 +1045,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>4005,4007,4023,4033,4047,4049,4051,4073</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["4005", "4007", "4023", "4033", "4047", "4049", "4051", "4073"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1094,29 +1078,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>4006,4008,4024,4034,4048,4050,4052,4074</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["4006", "4008", "4024", "4034", "4048", "4050", "4052", "4074"]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1127,29 +1111,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>בנים</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ב</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1160,814 +1140,332 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>בנות</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>מכירות</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["3009", "3019"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>מנהל בכיר</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["3010", "3020", "3024"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3005,3015,3023</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["4017", "4019", "4029", "4039", "4065", "4067", "4069", "4079"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3006,3016</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["4018", "4020", "4030", "4040", "4066", "4068", "4070", "4080"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>בנים</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>4009,4011,4025,4035,4053,4055,4057,4075</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["2005"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>בנות</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>4010,4012,4026,4036,4054,4056,4058,4076</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["2006"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>בנים</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["3005", "3015", "3023"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>זוטר</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>בנות</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["3006", "3016"]</t>
+          <t>מערכות מידע</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>בנים</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>["4009", "4011", "4025", "4035", "4053", "4055", "4057", "4075"]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ג</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="n">
         <v>6</v>
       </c>
-      <c r="C33" t="n">
-        <v>16</v>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>מנהל</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>בנות</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>["4010", "4012", "4026", "4036", "4054", "4056", "4058", "4076"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>7</v>
-      </c>
-      <c r="C34" t="n">
-        <v>12</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8</v>
-      </c>
-      <c r="C35" t="n">
-        <v>12</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>9</v>
-      </c>
-      <c r="C36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>10</v>
-      </c>
-      <c r="C37" t="n">
-        <v>6</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>["2007"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>["2008"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>["3007", "3017"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="n">
-        <v>6</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>["3008", "3018"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" t="n">
-        <v>18</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>["4013", "4015", "4027", "4037", "4059", "4061", "4063", "4077"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" t="n">
-        <v>18</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>["4014", "4016", "4028", "4038", "4060", "4062", "4064", "4078"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>7</v>
-      </c>
-      <c r="C44" t="n">
-        <v>14</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>8</v>
-      </c>
-      <c r="C45" t="n">
-        <v>14</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>9</v>
-      </c>
-      <c r="C46" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" t="n">
-        <v>6</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[]</t>
+          <t>מו"פ</t>
         </is>
       </c>
     </row>
